--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/18.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/18.xlsx
@@ -426,13 +426,13 @@
         <v>-10.76864494058244</v>
       </c>
       <c r="E2">
-        <v>-6.20974904378371</v>
+        <v>-6.587527930925594</v>
       </c>
       <c r="F2">
-        <v>-4.709778278115419</v>
+        <v>-4.533220049882733</v>
       </c>
       <c r="G2">
-        <v>-8.677126399648314</v>
+        <v>-8.346720712646892</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.88274817570867</v>
       </c>
       <c r="E3">
-        <v>-6.519813659088899</v>
+        <v>-6.887127242799058</v>
       </c>
       <c r="F3">
-        <v>-4.688808985680952</v>
+        <v>-4.37033651073546</v>
       </c>
       <c r="G3">
-        <v>-8.835254607331603</v>
+        <v>-8.73002229627479</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.12710343674481</v>
       </c>
       <c r="E4">
-        <v>-8.452548251666578</v>
+        <v>-7.510236209306483</v>
       </c>
       <c r="F4">
-        <v>-4.475408288841355</v>
+        <v>-4.121576122939962</v>
       </c>
       <c r="G4">
-        <v>-8.277440926146564</v>
+        <v>-8.227762879784262</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.3151561107193</v>
       </c>
       <c r="E5">
-        <v>-7.832292223783984</v>
+        <v>-8.156395108512951</v>
       </c>
       <c r="F5">
-        <v>-4.597792117298357</v>
+        <v>-4.165617104277201</v>
       </c>
       <c r="G5">
-        <v>-7.710927131284322</v>
+        <v>-7.58256734909016</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.45305746004681</v>
       </c>
       <c r="E6">
-        <v>-8.475081938328746</v>
+        <v>-8.866396434279556</v>
       </c>
       <c r="F6">
-        <v>-4.604800933893443</v>
+        <v>-4.087375317980579</v>
       </c>
       <c r="G6">
-        <v>-8.301720467131579</v>
+        <v>-7.893824840692437</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.48440972794474</v>
       </c>
       <c r="E7">
-        <v>-9.94540046456118</v>
+        <v>-10.21033883637993</v>
       </c>
       <c r="F7">
-        <v>-4.536563340720431</v>
+        <v>-3.697514968629229</v>
       </c>
       <c r="G7">
-        <v>-7.208555156245459</v>
+        <v>-8.326615769586899</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.38673788606061</v>
       </c>
       <c r="E8">
-        <v>-9.927236755316414</v>
+        <v>-9.484483323112475</v>
       </c>
       <c r="F8">
-        <v>-4.111563646142325</v>
+        <v>-4.012817281524208</v>
       </c>
       <c r="G8">
-        <v>-7.905315744259248</v>
+        <v>-7.458994615745785</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.11416088693837</v>
       </c>
       <c r="E9">
-        <v>-10.72284435372402</v>
+        <v>-10.86026995443479</v>
       </c>
       <c r="F9">
-        <v>-4.282906473206986</v>
+        <v>-3.732391721389296</v>
       </c>
       <c r="G9">
-        <v>-7.283178163246171</v>
+        <v>-8.096526233516473</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.63182918383212</v>
       </c>
       <c r="E10">
-        <v>-11.06166930745192</v>
+        <v>-11.64144077770594</v>
       </c>
       <c r="F10">
-        <v>-4.106929758891065</v>
+        <v>-3.786812146283613</v>
       </c>
       <c r="G10">
-        <v>-7.022250895477433</v>
+        <v>-7.857342628849669</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.8973221853336</v>
       </c>
       <c r="E11">
-        <v>-12.96460201258512</v>
+        <v>-12.18054655137108</v>
       </c>
       <c r="F11">
-        <v>-4.279817491161947</v>
+        <v>-3.534800416432127</v>
       </c>
       <c r="G11">
-        <v>-6.707997360162116</v>
+        <v>-8.110778132063036</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.88594240222771</v>
       </c>
       <c r="E12">
-        <v>-12.17333722075087</v>
+        <v>-11.91730635730521</v>
       </c>
       <c r="F12">
-        <v>-3.861539998057559</v>
+        <v>-3.255379665956812</v>
       </c>
       <c r="G12">
-        <v>-6.417205661083614</v>
+        <v>-6.869846621031545</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.58211325647007</v>
       </c>
       <c r="E13">
-        <v>-12.14390213970102</v>
+        <v>-12.95385141529091</v>
       </c>
       <c r="F13">
-        <v>-3.464977328050157</v>
+        <v>-3.161838762097887</v>
       </c>
       <c r="G13">
-        <v>-6.10297861013261</v>
+        <v>-6.638813579482426</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.99280502533403</v>
       </c>
       <c r="E14">
-        <v>-13.68670794937423</v>
+        <v>-13.77196552951664</v>
       </c>
       <c r="F14">
-        <v>-3.301456774370132</v>
+        <v>-2.595151793475342</v>
       </c>
       <c r="G14">
-        <v>-5.773794514435179</v>
+        <v>-6.162429386926842</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.13394720691845</v>
       </c>
       <c r="E15">
-        <v>-13.88590193554963</v>
+        <v>-13.35473910529394</v>
       </c>
       <c r="F15">
-        <v>-3.142887372656639</v>
+        <v>-2.465431943299147</v>
       </c>
       <c r="G15">
-        <v>-5.336597249427948</v>
+        <v>-5.916025482438887</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.03012745625752</v>
       </c>
       <c r="E16">
-        <v>-15.86399825226214</v>
+        <v>-14.68504174368321</v>
       </c>
       <c r="F16">
-        <v>-2.774289557800346</v>
+        <v>-2.3451356006972</v>
       </c>
       <c r="G16">
-        <v>-4.50615021144731</v>
+        <v>-5.475775894444448</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.7185265438544</v>
       </c>
       <c r="E17">
-        <v>-15.08303121032133</v>
+        <v>-15.78903842201317</v>
       </c>
       <c r="F17">
-        <v>-2.86896035479669</v>
+        <v>-2.242437923567729</v>
       </c>
       <c r="G17">
-        <v>-3.711622592567764</v>
+        <v>-4.380680535508932</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.25398527733033</v>
       </c>
       <c r="E18">
-        <v>-15.97258653049206</v>
+        <v>-16.07891962866617</v>
       </c>
       <c r="F18">
-        <v>-2.135571073299968</v>
+        <v>-1.600178168420383</v>
       </c>
       <c r="G18">
-        <v>-3.719293126582256</v>
+        <v>-4.686584874974208</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.70156782370489</v>
       </c>
       <c r="E19">
-        <v>-16.65974623336398</v>
+        <v>-16.8387024691991</v>
       </c>
       <c r="F19">
-        <v>-1.950355577340623</v>
+        <v>-1.401247393372887</v>
       </c>
       <c r="G19">
-        <v>-3.509258875388735</v>
+        <v>-4.211190535534866</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.14344793603091</v>
       </c>
       <c r="E20">
-        <v>-18.98915250664354</v>
+        <v>-18.30870400225099</v>
       </c>
       <c r="F20">
-        <v>-2.065532609393269</v>
+        <v>-1.31821930022289</v>
       </c>
       <c r="G20">
-        <v>-3.969719343900425</v>
+        <v>-4.726185620714969</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.663862837012307</v>
       </c>
       <c r="E21">
-        <v>-19.13995069109897</v>
+        <v>-18.50143132754344</v>
       </c>
       <c r="F21">
-        <v>-1.640983546682286</v>
+        <v>-0.6809198090835069</v>
       </c>
       <c r="G21">
-        <v>-4.462477494693244</v>
+        <v>-4.308643064574391</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.340924709305737</v>
       </c>
       <c r="E22">
-        <v>-19.42420753303444</v>
+        <v>-19.65487441356315</v>
       </c>
       <c r="F22">
-        <v>-1.257166965901761</v>
+        <v>-0.3629634070299587</v>
       </c>
       <c r="G22">
-        <v>-3.774814285821373</v>
+        <v>-4.109219111834234</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.240504619388172</v>
       </c>
       <c r="E23">
-        <v>-19.41856958289489</v>
+        <v>-19.94162191620284</v>
       </c>
       <c r="F23">
-        <v>-1.593222367339075</v>
+        <v>-0.7323291184686471</v>
       </c>
       <c r="G23">
-        <v>-3.099807292546135</v>
+        <v>-4.175542581167993</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.409610193717763</v>
       </c>
       <c r="E24">
-        <v>-19.6949921647971</v>
+        <v>-20.54843743323067</v>
       </c>
       <c r="F24">
-        <v>-0.8732700334831633</v>
+        <v>-0.281081774365436</v>
       </c>
       <c r="G24">
-        <v>-4.182272920249331</v>
+        <v>-4.094950660559975</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.867481436228949</v>
       </c>
       <c r="E25">
-        <v>-19.96277894676668</v>
+        <v>-20.65361124205882</v>
       </c>
       <c r="F25">
-        <v>-1.467189580472742</v>
+        <v>-0.3802713155440516</v>
       </c>
       <c r="G25">
-        <v>-3.747548632759936</v>
+        <v>-4.953146691250784</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.617632643709599</v>
       </c>
       <c r="E26">
-        <v>-20.72216781006093</v>
+        <v>-20.27439230018249</v>
       </c>
       <c r="F26">
-        <v>-1.231924954403654</v>
+        <v>-0.4806437653738649</v>
       </c>
       <c r="G26">
-        <v>-3.299598715841151</v>
+        <v>-4.212547859205967</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.640838039654676</v>
       </c>
       <c r="E27">
-        <v>-21.26132339694016</v>
+        <v>-20.57521430003802</v>
       </c>
       <c r="F27">
-        <v>-1.189317877040662</v>
+        <v>-0.3939526315686883</v>
       </c>
       <c r="G27">
-        <v>-4.99059889293656</v>
+        <v>-4.656045092374431</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.897768141287683</v>
       </c>
       <c r="E28">
-        <v>-21.14552125961601</v>
+        <v>-21.00241695249962</v>
       </c>
       <c r="F28">
-        <v>-0.8575724712001127</v>
+        <v>-0.5393650738235163</v>
       </c>
       <c r="G28">
-        <v>-5.38273632260877</v>
+        <v>-4.357112761814861</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.336754723347053</v>
       </c>
       <c r="E29">
-        <v>-21.18724661912269</v>
+        <v>-20.44976198460353</v>
       </c>
       <c r="F29">
-        <v>-0.8340103887948837</v>
+        <v>-0.5893321955603824</v>
       </c>
       <c r="G29">
-        <v>-4.254426260277747</v>
+        <v>-4.465834387870066</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.902875070889213</v>
       </c>
       <c r="E30">
-        <v>-21.11321512604529</v>
+        <v>-20.85685368399707</v>
       </c>
       <c r="F30">
-        <v>-1.227379702464493</v>
+        <v>-0.7109787770288927</v>
       </c>
       <c r="G30">
-        <v>-4.493828360950142</v>
+        <v>-4.601179421152089</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.538193522358863</v>
       </c>
       <c r="E31">
-        <v>-19.41873260795917</v>
+        <v>-20.60039261552067</v>
       </c>
       <c r="F31">
-        <v>-1.354071041416052</v>
+        <v>-0.9377998541612449</v>
       </c>
       <c r="G31">
-        <v>-4.616345030267491</v>
+        <v>-4.276964454309105</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.18839647905309</v>
       </c>
       <c r="E32">
-        <v>-21.04666014355456</v>
+        <v>-21.01725676182276</v>
       </c>
       <c r="F32">
-        <v>-1.568180820752446</v>
+        <v>-1.046918207029815</v>
       </c>
       <c r="G32">
-        <v>-3.951282915792224</v>
+        <v>-4.252211505311974</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.807501483876391</v>
       </c>
       <c r="E33">
-        <v>-19.69229319428853</v>
+        <v>-19.58123689772442</v>
       </c>
       <c r="F33">
-        <v>-1.457756960857064</v>
+        <v>-1.052187452079023</v>
       </c>
       <c r="G33">
-        <v>-4.277510694323085</v>
+        <v>-3.713340765702646</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.366109323563709</v>
       </c>
       <c r="E34">
-        <v>-18.29334794689099</v>
+        <v>-19.26394030942898</v>
       </c>
       <c r="F34">
-        <v>-1.482481242728421</v>
+        <v>-0.8723712548511259</v>
       </c>
       <c r="G34">
-        <v>-4.071247154498794</v>
+        <v>-3.942556317750705</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.847887144705808</v>
       </c>
       <c r="E35">
-        <v>-19.34102399398754</v>
+        <v>-18.68686328120952</v>
       </c>
       <c r="F35">
-        <v>-1.286216982350536</v>
+        <v>-0.9289421215231097</v>
       </c>
       <c r="G35">
-        <v>-5.012703405502273</v>
+        <v>-3.975956411696412</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.243886239833174</v>
       </c>
       <c r="E36">
-        <v>-19.73034596137498</v>
+        <v>-18.89871435223636</v>
       </c>
       <c r="F36">
-        <v>-1.009046077741225</v>
+        <v>-1.134814615406065</v>
       </c>
       <c r="G36">
-        <v>-3.895248621994519</v>
+        <v>-3.562773844031053</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.548663197751996</v>
       </c>
       <c r="E37">
-        <v>-18.79593610615827</v>
+        <v>-18.28935836129023</v>
       </c>
       <c r="F37">
-        <v>-1.466951839028138</v>
+        <v>-0.7846744830189506</v>
       </c>
       <c r="G37">
-        <v>-4.544916699712176</v>
+        <v>-3.740705735130262</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.762126422619358</v>
       </c>
       <c r="E38">
-        <v>-18.37753227869358</v>
+        <v>-18.2890458965837</v>
       </c>
       <c r="F38">
-        <v>-1.10800781788407</v>
+        <v>-0.8688979103311876</v>
       </c>
       <c r="G38">
-        <v>-4.035926944140309</v>
+        <v>-3.492510825505562</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.887300123106657</v>
       </c>
       <c r="E39">
-        <v>-17.43690935713834</v>
+        <v>-18.24194070995591</v>
       </c>
       <c r="F39">
-        <v>-1.198706593183991</v>
+        <v>-0.973785790873661</v>
       </c>
       <c r="G39">
-        <v>-4.426051562124644</v>
+        <v>-2.632543652951242</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.928749188002648</v>
       </c>
       <c r="E40">
-        <v>-17.46490891192777</v>
+        <v>-17.36135629679437</v>
       </c>
       <c r="F40">
-        <v>-1.387926417168468</v>
+        <v>-1.03079320716692</v>
       </c>
       <c r="G40">
-        <v>-3.657620973731173</v>
+        <v>-3.480602793200803</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.893269945731092</v>
       </c>
       <c r="E41">
-        <v>-16.23845323948239</v>
+        <v>-16.87240790123819</v>
       </c>
       <c r="F41">
-        <v>-0.9611366206329125</v>
+        <v>-0.8448694570781823</v>
       </c>
       <c r="G41">
-        <v>-3.43941629614673</v>
+        <v>-3.035185443619561</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.789574396616544</v>
       </c>
       <c r="E42">
-        <v>-15.67872932366033</v>
+        <v>-17.00619260884679</v>
       </c>
       <c r="F42">
-        <v>-1.44767158772798</v>
+        <v>-1.022381964558894</v>
       </c>
       <c r="G42">
-        <v>-4.298244641035541</v>
+        <v>-3.14239083981778</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.622592731473217</v>
       </c>
       <c r="E43">
-        <v>-16.03545986361456</v>
+        <v>-16.29964650874804</v>
       </c>
       <c r="F43">
-        <v>-1.234456445186609</v>
+        <v>-0.928598349050948</v>
       </c>
       <c r="G43">
-        <v>-3.928175307928111</v>
+        <v>-3.128807671470151</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.393599478087534</v>
       </c>
       <c r="E44">
-        <v>-15.78567376582547</v>
+        <v>-15.30375356192919</v>
       </c>
       <c r="F44">
-        <v>-1.284429365495295</v>
+        <v>-1.107179450481271</v>
       </c>
       <c r="G44">
-        <v>-3.470499008214948</v>
+        <v>-3.309070186629006</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.102300042444382</v>
       </c>
       <c r="E45">
-        <v>-14.40069886074159</v>
+        <v>-14.54925997903723</v>
       </c>
       <c r="F45">
-        <v>-1.833294837814011</v>
+        <v>-1.15449910999879</v>
       </c>
       <c r="G45">
-        <v>-3.222463004776133</v>
+        <v>-2.973562948951567</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.753266185228297</v>
       </c>
       <c r="E46">
-        <v>-14.98196925589215</v>
+        <v>-14.60732407276357</v>
       </c>
       <c r="F46">
-        <v>-1.46269154547554</v>
+        <v>-1.036354865909316</v>
       </c>
       <c r="G46">
-        <v>-3.213809238736478</v>
+        <v>-2.933412652651286</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.359571518453041</v>
       </c>
       <c r="E47">
-        <v>-14.52576625588543</v>
+        <v>-14.76088009788967</v>
       </c>
       <c r="F47">
-        <v>-1.762572142432601</v>
+        <v>-1.199839799791021</v>
       </c>
       <c r="G47">
-        <v>-3.993869773609408</v>
+        <v>-3.706378688433559</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.939631334879819</v>
       </c>
       <c r="E48">
-        <v>-14.14980328682062</v>
+        <v>-13.64532675389214</v>
       </c>
       <c r="F48">
-        <v>-1.437919218294821</v>
+        <v>-1.489065935213274</v>
       </c>
       <c r="G48">
-        <v>-3.444339077363627</v>
+        <v>-2.837317447282862</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.514302671854055</v>
       </c>
       <c r="E49">
-        <v>-13.23077665780797</v>
+        <v>-13.89931980403435</v>
       </c>
       <c r="F49">
-        <v>-1.85596311179162</v>
+        <v>-1.344157140339348</v>
       </c>
       <c r="G49">
-        <v>-3.200788863130524</v>
+        <v>-3.603659081441053</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.107599839914032</v>
       </c>
       <c r="E50">
-        <v>-13.22454094909941</v>
+        <v>-13.77398070045005</v>
       </c>
       <c r="F50">
-        <v>-1.991904829530241</v>
+        <v>-1.478920091263785</v>
       </c>
       <c r="G50">
-        <v>-4.088382538210062</v>
+        <v>-3.161661525401878</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.742237900657466</v>
       </c>
       <c r="E51">
-        <v>-13.3438526537795</v>
+        <v>-13.22341788754551</v>
       </c>
       <c r="F51">
-        <v>-2.07901677397604</v>
+        <v>-1.931582286890978</v>
       </c>
       <c r="G51">
-        <v>-3.356344776929799</v>
+        <v>-3.171887800572687</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.438126866362268</v>
       </c>
       <c r="E52">
-        <v>-12.48176705693929</v>
+        <v>-12.91604318580087</v>
       </c>
       <c r="F52">
-        <v>-1.987368689632511</v>
+        <v>-1.576475263556678</v>
       </c>
       <c r="G52">
-        <v>-3.028269713988024</v>
+        <v>-3.495235404484382</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.213259865127132</v>
       </c>
       <c r="E53">
-        <v>-12.81463706734711</v>
+        <v>-11.9351938296355</v>
       </c>
       <c r="F53">
-        <v>-2.005309470842342</v>
+        <v>-1.462822427525183</v>
       </c>
       <c r="G53">
-        <v>-2.931720963880719</v>
+        <v>-3.213398731089608</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.081816708204627</v>
       </c>
       <c r="E54">
-        <v>-13.0125857231704</v>
+        <v>-12.43941223954555</v>
       </c>
       <c r="F54">
-        <v>-1.915099432310074</v>
+        <v>-1.713648763623262</v>
       </c>
       <c r="G54">
-        <v>-2.713648708117848</v>
+        <v>-3.347542036340876</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.052727478393424</v>
       </c>
       <c r="E55">
-        <v>-11.06033793609367</v>
+        <v>-11.44197055461608</v>
       </c>
       <c r="F55">
-        <v>-2.280778908806304</v>
+        <v>-1.629467583048568</v>
       </c>
       <c r="G55">
-        <v>-4.020913620119715</v>
+        <v>-3.733266939303519</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.131255123916801</v>
       </c>
       <c r="E56">
-        <v>-11.58612546770225</v>
+        <v>-11.41120863068197</v>
       </c>
       <c r="F56">
-        <v>-2.208733310682623</v>
+        <v>-2.087352635150411</v>
       </c>
       <c r="G56">
-        <v>-4.735660402048364</v>
+        <v>-3.710490385993334</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.316161495448203</v>
       </c>
       <c r="E57">
-        <v>-10.34670930264692</v>
+        <v>-11.14730275093697</v>
       </c>
       <c r="F57">
-        <v>-2.431141674660262</v>
+        <v>-1.649128883354014</v>
       </c>
       <c r="G57">
-        <v>-4.273594318950127</v>
+        <v>-3.725430878012065</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.600085144083016</v>
       </c>
       <c r="E58">
-        <v>-10.58776903102323</v>
+        <v>-11.39246980523824</v>
       </c>
       <c r="F58">
-        <v>-2.05359335001672</v>
+        <v>-1.946872292411851</v>
       </c>
       <c r="G58">
-        <v>-4.478414460919296</v>
+        <v>-3.732108248364775</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.975395202742997</v>
       </c>
       <c r="E59">
-        <v>-10.07286342245508</v>
+        <v>-10.95559886077026</v>
       </c>
       <c r="F59">
-        <v>-2.032793044532425</v>
+        <v>-1.988536687670458</v>
       </c>
       <c r="G59">
-        <v>-4.016603289827583</v>
+        <v>-3.929509457780437</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.43210552119126</v>
       </c>
       <c r="E60">
-        <v>-9.679950375179558</v>
+        <v>-9.863752078202882</v>
       </c>
       <c r="F60">
-        <v>-2.227112298248535</v>
+        <v>-2.127718978688831</v>
       </c>
       <c r="G60">
-        <v>-3.862941008076772</v>
+        <v>-3.906398539370785</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.958191021621657</v>
       </c>
       <c r="E61">
-        <v>-9.528142341020425</v>
+        <v>-9.413241370023805</v>
       </c>
       <c r="F61">
-        <v>-2.464039457695042</v>
+        <v>-2.163083639849148</v>
       </c>
       <c r="G61">
-        <v>-4.534336196168665</v>
+        <v>-4.233851219751177</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.540155400583279</v>
       </c>
       <c r="E62">
-        <v>-9.53783327539684</v>
+        <v>-9.795757040977712</v>
       </c>
       <c r="F62">
-        <v>-2.43729561609566</v>
+        <v>-2.258022827883999</v>
       </c>
       <c r="G62">
-        <v>-4.307570447819668</v>
+        <v>-4.184600233763439</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.16165454160212</v>
       </c>
       <c r="E63">
-        <v>-10.60783469935122</v>
+        <v>-10.02087654084702</v>
       </c>
       <c r="F63">
-        <v>-2.481233879874951</v>
+        <v>-2.214195565336682</v>
       </c>
       <c r="G63">
-        <v>-5.364472042868612</v>
+        <v>-4.610876009036615</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.803178895534989</v>
       </c>
       <c r="E64">
-        <v>-9.362522461137898</v>
+        <v>-9.361358643317926</v>
       </c>
       <c r="F64">
-        <v>-2.657256154398026</v>
+        <v>-2.267701472618308</v>
       </c>
       <c r="G64">
-        <v>-4.50419698957914</v>
+        <v>-4.236026248170478</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.44698235085318</v>
       </c>
       <c r="E65">
-        <v>-8.388615255626288</v>
+        <v>-9.783054671386198</v>
       </c>
       <c r="F65">
-        <v>-2.846512426548227</v>
+        <v>-2.374912095358232</v>
       </c>
       <c r="G65">
-        <v>-4.655598168726629</v>
+        <v>-4.699479449849669</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.07397435701935</v>
       </c>
       <c r="E66">
-        <v>-9.11535834979925</v>
+        <v>-9.566878907682037</v>
       </c>
       <c r="F66">
-        <v>-2.396088479643398</v>
+        <v>-2.405537666607132</v>
       </c>
       <c r="G66">
-        <v>-4.692424677305482</v>
+        <v>-4.506699762006829</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.66681168609268</v>
       </c>
       <c r="E67">
-        <v>-7.808445279659591</v>
+        <v>-9.292023177786485</v>
       </c>
       <c r="F67">
-        <v>-2.55725564153207</v>
+        <v>-2.099460053109729</v>
       </c>
       <c r="G67">
-        <v>-5.303031628205278</v>
+        <v>-4.150266565975658</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.21234933412311</v>
       </c>
       <c r="E68">
-        <v>-9.060504944144338</v>
+        <v>-9.616488340436065</v>
       </c>
       <c r="F68">
-        <v>-2.856240773326704</v>
+        <v>-2.107768578159808</v>
       </c>
       <c r="G68">
-        <v>-4.589261457210713</v>
+        <v>-4.806757678049752</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.70118376574061</v>
       </c>
       <c r="E69">
-        <v>-8.19406748378276</v>
+        <v>-8.435177025373154</v>
       </c>
       <c r="F69">
-        <v>-2.521524013612313</v>
+        <v>-2.52506197078967</v>
       </c>
       <c r="G69">
-        <v>-4.936193387544177</v>
+        <v>-4.68566785385983</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.1264106907066</v>
       </c>
       <c r="E70">
-        <v>-8.401928969208837</v>
+        <v>-8.736039781494757</v>
       </c>
       <c r="F70">
-        <v>-2.690020570280955</v>
+        <v>-2.34083306040706</v>
       </c>
       <c r="G70">
-        <v>-4.640939073078736</v>
+        <v>-4.817669236147189</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.4874536311456</v>
       </c>
       <c r="E71">
-        <v>-8.560262534413024</v>
+        <v>-8.87688438008132</v>
       </c>
       <c r="F71">
-        <v>-2.788950004095092</v>
+        <v>-2.855033842020825</v>
       </c>
       <c r="G71">
-        <v>-3.979127914323033</v>
+        <v>-4.331230916788838</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.78229501062559</v>
       </c>
       <c r="E72">
-        <v>-9.382841724010314</v>
+        <v>-8.140255627149614</v>
       </c>
       <c r="F72">
-        <v>-2.883684585381451</v>
+        <v>-2.624572090153169</v>
       </c>
       <c r="G72">
-        <v>-4.322507629292859</v>
+        <v>-3.890994570976556</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.00850802131286</v>
       </c>
       <c r="E73">
-        <v>-8.894916763579864</v>
+        <v>-8.948769376479079</v>
       </c>
       <c r="F73">
-        <v>-2.541553937412005</v>
+        <v>-2.474012172857345</v>
       </c>
       <c r="G73">
-        <v>-4.097145552252512</v>
+        <v>-4.080083000543109</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.16386012774269</v>
       </c>
       <c r="E74">
-        <v>-8.788198745115103</v>
+        <v>-8.609627429570638</v>
       </c>
       <c r="F74">
-        <v>-2.711251626814706</v>
+        <v>-2.680496830250969</v>
       </c>
       <c r="G74">
-        <v>-4.418500207749566</v>
+        <v>-3.618904143649396</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.24734540737896</v>
       </c>
       <c r="E75">
-        <v>-9.05087740840403</v>
+        <v>-9.612947073762069</v>
       </c>
       <c r="F75">
-        <v>-2.945853558961554</v>
+        <v>-2.728622491251412</v>
       </c>
       <c r="G75">
-        <v>-3.649708769892315</v>
+        <v>-3.786123109383523</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.25997535049926</v>
       </c>
       <c r="E76">
-        <v>-9.222737525469128</v>
+        <v>-9.465033527249531</v>
       </c>
       <c r="F76">
-        <v>-3.059410304374325</v>
+        <v>-2.624952310791054</v>
       </c>
       <c r="G76">
-        <v>-3.569275755470182</v>
+        <v>-3.462954274930949</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.21150257289591</v>
       </c>
       <c r="E77">
-        <v>-10.80481426173686</v>
+        <v>-10.00083351488907</v>
       </c>
       <c r="F77">
-        <v>-2.73245369048936</v>
+        <v>-2.741763711729424</v>
       </c>
       <c r="G77">
-        <v>-4.697708307986159</v>
+        <v>-3.46726460522308</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.11329261483622</v>
       </c>
       <c r="E78">
-        <v>-10.49640706791848</v>
+        <v>-10.48253635203298</v>
       </c>
       <c r="F78">
-        <v>-2.826716930723527</v>
+        <v>-2.936478096696669</v>
       </c>
       <c r="G78">
-        <v>-4.394078313306363</v>
+        <v>-3.351537864806777</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.9812442936499</v>
       </c>
       <c r="E79">
-        <v>-10.97753931733742</v>
+        <v>-10.509702667605</v>
       </c>
       <c r="F79">
-        <v>-3.392135668852385</v>
+        <v>-2.946746539021772</v>
       </c>
       <c r="G79">
-        <v>-4.021804156869778</v>
+        <v>-3.065910616769537</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.83279447360111</v>
       </c>
       <c r="E80">
-        <v>-11.62827650376565</v>
+        <v>-11.48559787320598</v>
       </c>
       <c r="F80">
-        <v>-3.447829294444805</v>
+        <v>-2.842638980572736</v>
       </c>
       <c r="G80">
-        <v>-3.484436404935279</v>
+        <v>-2.935329458518525</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.68261810613754</v>
       </c>
       <c r="E81">
-        <v>-11.53755305549598</v>
+        <v>-12.53228218449486</v>
       </c>
       <c r="F81">
-        <v>-3.19997514058797</v>
+        <v>-3.165412339073563</v>
       </c>
       <c r="G81">
-        <v>-4.126129378448831</v>
+        <v>-2.668542525145277</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.54060432541404</v>
       </c>
       <c r="E82">
-        <v>-12.97549752104758</v>
+        <v>-12.95881462280332</v>
       </c>
       <c r="F82">
-        <v>-3.457217182220731</v>
+        <v>-2.71268470242155</v>
       </c>
       <c r="G82">
-        <v>-3.074233328255265</v>
+        <v>-2.385821936091518</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.415912621148</v>
       </c>
       <c r="E83">
-        <v>-14.18508009934038</v>
+        <v>-12.74139805722106</v>
       </c>
       <c r="F83">
-        <v>-3.569254701816767</v>
+        <v>-3.379697732299351</v>
       </c>
       <c r="G83">
-        <v>-2.585517353565896</v>
+        <v>-2.789446958785001</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.30857100283246</v>
       </c>
       <c r="E84">
-        <v>-14.54388920886413</v>
+        <v>-13.85282143292359</v>
       </c>
       <c r="F84">
-        <v>-3.348915599611321</v>
+        <v>-3.193590084647191</v>
       </c>
       <c r="G84">
-        <v>-3.313896962025263</v>
+        <v>-2.865354457454949</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.21654000986937</v>
       </c>
       <c r="E85">
-        <v>-15.03032882982006</v>
+        <v>-14.65903471745716</v>
       </c>
       <c r="F85">
-        <v>-3.731953515033215</v>
+        <v>-3.702425530593024</v>
       </c>
       <c r="G85">
-        <v>-3.223214498613547</v>
+        <v>-2.41252148586574</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.13460343249756</v>
       </c>
       <c r="E86">
-        <v>-15.67023390642194</v>
+        <v>-15.97888563783673</v>
       </c>
       <c r="F86">
-        <v>-3.883436233615758</v>
+        <v>-3.268364324995694</v>
       </c>
       <c r="G86">
-        <v>-3.216699344992261</v>
+        <v>-1.834410849979431</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.05339155711235</v>
       </c>
       <c r="E87">
-        <v>-17.64155109754497</v>
+        <v>-17.91564604380723</v>
       </c>
       <c r="F87">
-        <v>-3.838659662024833</v>
+        <v>-3.531797584596979</v>
       </c>
       <c r="G87">
-        <v>-3.463450856761839</v>
+        <v>-2.851251533457654</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.96090573693378</v>
       </c>
       <c r="E88">
-        <v>-19.31594530493307</v>
+        <v>-17.81127830335245</v>
       </c>
       <c r="F88">
-        <v>-3.745053317141087</v>
+        <v>-3.498571768070691</v>
       </c>
       <c r="G88">
-        <v>-3.43996253616071</v>
+        <v>-2.284340473130699</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.8536241961671</v>
       </c>
       <c r="E89">
-        <v>-19.87341856917332</v>
+        <v>-19.7201433094357</v>
       </c>
       <c r="F89">
-        <v>-4.025107768679543</v>
+        <v>-3.708492493451128</v>
       </c>
       <c r="G89">
-        <v>-3.235079493826295</v>
+        <v>-2.444027947762984</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.73045960542543</v>
       </c>
       <c r="E90">
-        <v>-21.40750706638177</v>
+        <v>-21.56777881846124</v>
       </c>
       <c r="F90">
-        <v>-3.935955555320649</v>
+        <v>-3.622130221504862</v>
       </c>
       <c r="G90">
-        <v>-2.870465939767584</v>
+        <v>-1.548171151017426</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.60088345420133</v>
       </c>
       <c r="E91">
-        <v>-23.84236791387795</v>
+        <v>-22.00604000444957</v>
       </c>
       <c r="F91">
-        <v>-3.880663687918588</v>
+        <v>-3.425941342560633</v>
       </c>
       <c r="G91">
-        <v>-2.581574493828624</v>
+        <v>-2.669317192801467</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.4804589092906</v>
       </c>
       <c r="E92">
-        <v>-25.54426354391463</v>
+        <v>-25.12013119683023</v>
       </c>
       <c r="F92">
-        <v>-4.164483897670172</v>
+        <v>-3.429838811190805</v>
       </c>
       <c r="G92">
-        <v>-3.478523770602141</v>
+        <v>-2.662182967164338</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.38979168523756</v>
       </c>
       <c r="E93">
-        <v>-28.32670741386955</v>
+        <v>-26.79729683031103</v>
       </c>
       <c r="F93">
-        <v>-4.189523787521995</v>
+        <v>-3.835747950603993</v>
       </c>
       <c r="G93">
-        <v>-3.333720508714419</v>
+        <v>-2.621529467942088</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.35196673495814</v>
       </c>
       <c r="E94">
-        <v>-29.36186675880891</v>
+        <v>-28.98667363032541</v>
       </c>
       <c r="F94">
-        <v>-4.205527017376679</v>
+        <v>-3.721897134763229</v>
       </c>
       <c r="G94">
-        <v>-4.067241394396276</v>
+        <v>-3.012816087410706</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.3925496053356</v>
       </c>
       <c r="E95">
-        <v>-31.98245391078168</v>
+        <v>-30.91466691061705</v>
       </c>
       <c r="F95">
-        <v>-3.557636020625101</v>
+        <v>-3.476105615739366</v>
       </c>
       <c r="G95">
-        <v>-3.777151530972098</v>
+        <v>-2.89846653393874</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.53483228273418</v>
       </c>
       <c r="E96">
-        <v>-35.22696062610925</v>
+        <v>-33.1653049070072</v>
       </c>
       <c r="F96">
-        <v>-4.361711549337511</v>
+        <v>-3.790358387134997</v>
       </c>
       <c r="G96">
-        <v>-4.21916563973897</v>
+        <v>-3.469694545648905</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.78436278013717</v>
       </c>
       <c r="E97">
-        <v>-36.32783039313691</v>
+        <v>-36.15429700492597</v>
       </c>
       <c r="F97">
-        <v>-4.189641415693193</v>
+        <v>-3.878128055298619</v>
       </c>
       <c r="G97">
-        <v>-3.897046248222344</v>
+        <v>-3.37855191640723</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.16423583009127</v>
       </c>
       <c r="E98">
-        <v>-39.44462282026315</v>
+        <v>-38.35384475756158</v>
       </c>
       <c r="F98">
-        <v>-3.887910245958278</v>
+        <v>-3.448738841853078</v>
       </c>
       <c r="G98">
-        <v>-5.227362488814156</v>
+        <v>-3.965511640520011</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.6455769838752</v>
       </c>
       <c r="E99">
-        <v>-41.69052856131528</v>
+        <v>-40.81434582488919</v>
       </c>
       <c r="F99">
-        <v>-4.655612990381165</v>
+        <v>-3.870119399248353</v>
       </c>
       <c r="G99">
-        <v>-4.865741667922946</v>
+        <v>-4.643130654225734</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.25418748005844</v>
       </c>
       <c r="E100">
-        <v>-44.18491846387928</v>
+        <v>-43.62442470747592</v>
       </c>
       <c r="F100">
-        <v>-4.289082780562259</v>
+        <v>-3.867629326835538</v>
       </c>
       <c r="G100">
-        <v>-5.148207344970182</v>
+        <v>-4.466069436603354</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.90753572902551</v>
       </c>
       <c r="E101">
-        <v>-46.29024905054831</v>
+        <v>-45.33964084380617</v>
       </c>
       <c r="F101">
-        <v>-4.146519922173061</v>
+        <v>-3.869991002300919</v>
       </c>
       <c r="G101">
-        <v>-5.26463592104081</v>
+        <v>-4.116210984013175</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.68663207780189</v>
       </c>
       <c r="E102">
-        <v>-49.88884280912813</v>
+        <v>-47.99613653042275</v>
       </c>
       <c r="F102">
-        <v>-4.322287059536075</v>
+        <v>-3.588135680028776</v>
       </c>
       <c r="G102">
-        <v>-6.050486600061927</v>
+        <v>-5.114317290284663</v>
       </c>
     </row>
   </sheetData>
